--- a/Karcher/Basic/asset-model.xlsx
+++ b/Karcher/Basic/asset-model.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Projeke\Karcher\Basic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675D9B80-B43C-415B-B778-4C4B59FD3FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36008B36-2430-4809-B6BF-22F75EBF6F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockWindows="1"/>
   <bookViews>
-    <workbookView xWindow="-12780" yWindow="-17388" windowWidth="30936" windowHeight="16776" tabRatio="929" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13536" yWindow="-17388" windowWidth="30936" windowHeight="16776" tabRatio="711" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dropdownlist" sheetId="1" state="hidden" r:id="rId1"/>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14700" uniqueCount="3020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14713" uniqueCount="3022">
   <si>
     <t>Action</t>
   </si>
@@ -9199,13 +9199,19 @@
   </si>
   <si>
     <t>Sharedien ID</t>
+  </si>
+  <si>
+    <t>atxkarcherthumbnailurl</t>
+  </si>
+  <si>
+    <t>Kärcher Thumbnail URL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -9292,6 +9298,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF292A2E"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -9476,7 +9488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -9541,6 +9553,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10275,7 +10288,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AX582"/>
+  <dimension ref="A1:AX586"/>
   <sheetFormatPr defaultRowHeight="21.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.25" bestFit="1" customWidth="1"/>
@@ -17042,6 +17055,38 @@
       </c>
       <c r="H582" t="s">
         <v>3014</v>
+      </c>
+    </row>
+    <row r="583" spans="2:8" ht="21.75" customHeight="1">
+      <c r="B583" t="s">
+        <v>204</v>
+      </c>
+      <c r="D583" t="s">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="584" spans="2:8" ht="21.75" customHeight="1">
+      <c r="B584" t="s">
+        <v>207</v>
+      </c>
+      <c r="D584" t="s">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="585" spans="2:8" ht="21.75" customHeight="1">
+      <c r="B585" t="s">
+        <v>210</v>
+      </c>
+      <c r="D585" t="s">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="586" spans="2:8" ht="21.75" customHeight="1">
+      <c r="B586" t="s">
+        <v>213</v>
+      </c>
+      <c r="D586" t="s">
+        <v>3020</v>
       </c>
     </row>
   </sheetData>
@@ -21520,6 +21565,21 @@
       </c>
     </row>
     <row r="162" spans="2:24" ht="21.75" customHeight="1">
+      <c r="B162" t="s">
+        <v>3020</v>
+      </c>
+      <c r="D162" t="s">
+        <v>94</v>
+      </c>
+      <c r="F162" s="46" t="s">
+        <v>3021</v>
+      </c>
+      <c r="G162" t="s">
+        <v>3012</v>
+      </c>
+      <c r="H162" t="s">
+        <v>97</v>
+      </c>
       <c r="P162">
         <v>30</v>
       </c>
